--- a/billing.xlsx
+++ b/billing.xlsx
@@ -7,172 +7,43 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="4" r:id="rId7"/>
+    <sheet name="Sessions" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OverlayTimer</author>
-  </authors>
-  <commentList>
-    <comment ref="A4" authorId="0">
-      <text>
-        <t>{"version":1,"session":{"id":"S-20261014114306.926583900","pc_id":"8d438118574e8aae","pc_name":"PC2-PG-SKV","pc_address":"http://192.168.1.5:18081","category":"PC Lite","customer_name":"sarvagya","players":4,"status":"closed","started_at":"2026-10-14T17:13:06.9500852+05:30","expected_end_at":"2026-10-14T17:28:06.9500852+05:30","ended_at":"2026-10-14T17:14:24.6635964+05:30","purchased_minutes":15,"additional_minutes":0,"pricing_snapshot":"{\"category\":\"PC Lite\",\"players\":4,\"duration_minutes\":15,\"amount\":30}","estimated_amount":30,"final_amount":30,"amount_paid":30,"payment_status":"paid","payment_at":"2026-10-14T17:13:06.9500852+05:30","created_at":"2026-10-14T17:13:06.9625238+05:30","updated_at":"2026-10-14T17:14:24.6635964+05:30"}}</t>
-      </text>
-    </comment>
-    <comment ref="A7" authorId="0">
-      <text>
-        <t>{"version":1,"session":{"id":"S-20261014120230.779853600","pc_id":"27baec0088a7fcf9","pc_name":"PC3","pc_address":"http://192.168.1.13:18081","category":"PC Lite","customer_name":"sarvagya","players":2,"status":"closed","started_at":"2026-10-14T17:32:30.9197814+05:30","expected_end_at":"2026-10-14T19:47:30.9197814+05:30","ended_at":"2026-10-14T17:33:02.781662+05:30","purchased_minutes":135,"additional_minutes":0,"pricing_snapshot":"{\"category\":\"PC Lite\",\"players\":2,\"duration_minutes\":30,\"amount\":40}","estimated_amount":170,"final_amount":170,"amount_paid":170,"payment_status":"paid","payment_at":"2026-10-14T17:32:47.4110782+05:30","created_at":"2026-10-14T17:32:30.9469431+05:30","updated_at":"2026-10-14T17:33:02.781662+05:30"},"payments":[{"id":"P-20261014120240.506224800","timestamp":"2026-10-14T17:32:40.5062248+05:30","amount":20,"status":"paid"},{"id":"P-20261014120244.686649300","timestamp":"2026-10-14T17:32:44.6866493+05:30","amount":40,"status":"paid"},{"id":"P-20261014120247.411078200","timestamp":"2026-10-14T17:32:47.4110782+05:30","amount":70,"status":"paid"}]}</t>
-      </text>
-    </comment>
-    <comment ref="A6" authorId="0">
-      <text>
-        <t>{"version":1,"session":{"id":"S-20261014114427.669145200","pc_id":"8d438118574e8aae","pc_name":"PC2-PG-SKV","pc_address":"http://192.168.1.5:18081","category":"PC Lite","customer_name":"sarvagyasharma660@gmail.com","players":2,"status":"closed","started_at":"2026-10-14T17:14:27.6811368+05:30","expected_end_at":"2026-10-14T17:29:27.6811368+05:30","ended_at":"2026-10-14T18:15:47.6383378+05:30","purchased_minutes":15,"additional_minutes":0,"pricing_snapshot":"{\"category\":\"PC Lite\",\"players\":2,\"duration_minutes\":15,\"amount\":20}","estimated_amount":20,"final_amount":20,"amount_paid":20,"payment_status":"paid","payment_at":"2026-10-14T17:14:27.6811368+05:30","created_at":"2026-10-14T17:14:27.6948538+05:30","updated_at":"2026-10-14T18:15:47.6383378+05:30"}}</t>
-      </text>
-    </comment>
-    <comment ref="A2" authorId="0">
-      <text>
-        <t>{"version":1,"session":{"id":"S-20261014113501.641537600","pc_id":"8d438118574e8aae","pc_name":"PC2-PG-SKV","pc_address":"http://192.168.1.5:18081","category":"PC Lite","customer_name":"kh","players":1,"status":"closed","started_at":"2026-10-14T17:05:01.715265+05:30","expected_end_at":"2026-10-14T17:20:01.715265+05:30","ended_at":"2026-10-14T17:05:08.689798+05:30","purchased_minutes":15,"additional_minutes":0,"pricing_snapshot":"{\"category\":\"PC Lite\",\"players\":1,\"duration_minutes\":15,\"amount\":15}","estimated_amount":15,"final_amount":15,"amount_paid":15,"payment_status":"paid","payment_at":"2026-10-14T17:05:01.715265+05:30","created_at":"2026-10-14T17:05:01.7300656+05:30","updated_at":"2026-10-14T21:52:40.1735121+05:30"}}</t>
-      </text>
-    </comment>
-    <comment ref="A3" authorId="0">
-      <text>
-        <t>{"version":1,"session":{"id":"S-20261014113524.793748500","pc_id":"8d438118574e8aae","pc_name":"PC2-PG-SKV","pc_address":"http://192.168.1.5:18081","category":"PC Lite","customer_name":"ijg","players":1,"status":"closed","started_at":"2026-10-14T17:05:24.806629+05:30","expected_end_at":"2026-10-14T19:05:24.806629+05:30","ended_at":"2026-10-14T17:05:55.3283885+05:30","purchased_minutes":120,"additional_minutes":0,"pricing_snapshot":"{\"category\":\"PC Lite\",\"players\":1,\"duration_minutes\":15,\"amount\":15}","estimated_amount":110,"final_amount":110,"amount_paid":110,"payment_status":"paid","payment_at":"2026-10-14T17:05:50.7426427+05:30","created_at":"2026-10-14T17:05:24.817919+05:30","updated_at":"2026-10-14T21:52:40.8479688+05:30"},"payments":[{"id":"P-20261014113535.678862900","timestamp":"2026-10-14T17:05:35.6788629+05:30","amount":15,"status":"paid"},{"id":"P-20261014113549.272387400","timestamp":"2026-10-14T17:05:49.2723874+05:30","amount":30,"status":"paid"},{"id":"P-20261014113550.742642700","timestamp":"2026-10-14T17:05:50.7426427+05:30","amount":50,"status":"paid"}]}</t>
-      </text>
-    </comment>
-    <comment ref="A5" authorId="0">
-      <text>
-        <t>{"version":1,"session":{"id":"S-20261014114314.963490700","pc_id":"3b1688537d7b1560","pc_name":"PC-4","pc_address":"http://192.168.1.7:18081","category":"PC Lite","customer_name":"sarvagyasharma660@gmail.com","players":4,"status":"open","started_at":"2026-10-14T17:13:14.9901373+05:30","expected_end_at":"2026-10-14T21:43:14.9901373+05:30","purchased_minutes":270,"additional_minutes":0,"pricing_snapshot":"{\"category\":\"PC Lite\",\"players\":4,\"duration_minutes\":15,\"amount\":30}","estimated_amount":520,"final_amount":520,"amount_paid":520,"payment_status":"paid","payment_at":"2026-10-22T17:13:15.3072633+05:30","created_at":"2026-10-14T17:13:15.0086751+05:30","updated_at":"2026-10-22T17:13:15.3072633+05:30"},"payments":[{"id":"E-c17cbbb15e5faed46e8cdb8a38733f2a957dce6f6ea34872c4453e5b20631eac","timestamp":"2026-10-15T16:24:40.2321159+05:30","amount":60,"status":"paid","extension_minutes":30,"remaining_seconds":1800},{"id":"E-8a8832590d76e1cb55e0ff85c5cf8ced404f6a93dfe9da62f7cd3f1d533e5949","timestamp":"2026-10-15T16:24:40.4714796+05:30","amount":60,"status":"paid","extension_minutes":30,"remaining_seconds":3600},{"id":"E-35c8f4ff433dd99a6931d4746a2d80fba488814d6f209f7d19d8f6ceb89e775f","timestamp":"2026-10-15T16:24:40.9236414+05:30","amount":60,"status":"paid","extension_minutes":30,"remaining_seconds":5399},{"id":"E-244504026f3e79d76fa85147a6c27d24873ddf497c20a51068bfef7a6bbe8183","timestamp":"2026-10-15T16:29:49.0795075+05:30","amount":30,"status":"paid","extension_minutes":15,"remaining_seconds":5991},{"id":"E-2d96aaa4b9aad4394ef70cf452451210bf905de77d9dc785b1fa15862f12eb9b","timestamp":"2026-10-15T16:29:50.1116029+05:30","amount":30,"status":"paid","extension_minutes":15,"remaining_seconds":6890},{"id":"E-8e05150fe6b32549a78f644d7a426939c4c9e9b255ec2ea74c0225c88214273a","timestamp":"2026-10-15T16:30:01.5528613+05:30","amount":30,"status":"paid","extension_minutes":15,"remaining_seconds":7779},{"id":"E-e2ae24e95aa29d96c0c2fdf6d865410881b7fa28ce37963b5ca3ebd6be9dd371","timestamp":"2026-10-15T16:30:24.8003972+05:30","amount":110,"status":"paid","extension_minutes":60,"remaining_seconds":11356},{"id":"E-66a631a3643aff4181796713ea2940e6dabee45dad6260bb02e45261501b1fc8","timestamp":"2026-10-22T17:13:15.3072633+05:30","amount":110,"status":"paid","extension_minutes":60,"remaining_seconds":3660}]}</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t>Session ID</t>
-  </si>
-  <si>
-    <t>System ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Customer</t>
   </si>
   <si>
     <t>System</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
     <t>Players</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Expected End</t>
-  </si>
-  <si>
-    <t>End</t>
+    <t>Start Time</t>
   </si>
   <si>
     <t>Purchased Minutes</t>
   </si>
   <si>
-    <t>Additional Minutes</t>
-  </si>
-  <si>
-    <t>Pricing Snapshot</t>
-  </si>
-  <si>
-    <t>Estimated Amount</t>
-  </si>
-  <si>
-    <t>Final Amount</t>
-  </si>
-  <si>
     <t>Amount Paid</t>
-  </si>
-  <si>
-    <t>Payment Status</t>
-  </si>
-  <si>
-    <t>Payment At</t>
-  </si>
-  <si>
-    <t>Created At</t>
-  </si>
-  <si>
-    <t>Updated At</t>
-  </si>
-  <si>
-    <t>Payment ID</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Collected Amount</t>
-  </si>
-  <si>
-    <t>Payment Count</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Start Time</t>
-  </si>
-  <si>
-    <t>kh</t>
-  </si>
-  <si>
-    <t>PC2-PG-SKV</t>
-  </si>
-  <si>
-    <t>ijg</t>
-  </si>
-  <si>
-    <t>sarvagya</t>
-  </si>
-  <si>
-    <t>sarvagyasharma660@gmail.com</t>
-  </si>
-  <si>
-    <t>PC-4</t>
-  </si>
-  <si>
-    <t>PC3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
-    <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="&quot;₹&quot;#,##0"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -211,19 +82,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,9 +352,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="14"/>
     <col customWidth="true" max="2" min="2" width="12"/>
@@ -506,187 +369,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>46309</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.7118171296296296</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.7118171296296296</v>
-      </c>
-      <c r="G2">
-        <v>15</v>
-      </c>
-      <c r="H2" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>46309</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.7120833333333333</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.7120833333333333</v>
-      </c>
-      <c r="G3">
-        <v>120</v>
-      </c>
-      <c r="H3" s="4">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>46309</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.7174305555555556</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.7174305555555556</v>
-      </c>
-      <c r="G4">
-        <v>15</v>
-      </c>
-      <c r="H4" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>46309</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.7175347222222223</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.7175231481481481</v>
-      </c>
-      <c r="G5">
-        <v>270</v>
-      </c>
-      <c r="H5" s="4">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>46309</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.7183680555555556</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.7183680555555556</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>46309</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.7309027777777778</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.7309027777777778</v>
-      </c>
-      <c r="G7">
-        <v>135</v>
-      </c>
-      <c r="H7" s="4">
-        <v>170</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>